--- a/output/pdf_financials_xlsx/SWP.xlsx
+++ b/output/pdf_financials_xlsx/SWP.xlsx
@@ -2246,19 +2246,19 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.074</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.304</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.898</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>9.065</v>
@@ -2384,19 +2384,19 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.074</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.304</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.898</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>9.065</v>
@@ -3212,19 +3212,19 @@
         <v>2.219</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.828</v>
+        <v>1.754</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.748</v>
+        <v>0.248</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.531</v>
+        <v>0.227</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.746</v>
+        <v>0.152</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.809</v>
+        <v>0.911</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.354</v>
@@ -13516,7 +13516,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
